--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.76690759767084</v>
+        <v>2.399622484621511</v>
       </c>
       <c r="D2" t="n">
-        <v>15.09651762131445</v>
+        <v>2.453184113463597</v>
       </c>
       <c r="E2" t="n">
-        <v>5.308409623324787</v>
+        <v>0.862616563790278</v>
       </c>
       <c r="F2" t="n">
-        <v>5.040874071203608</v>
+        <v>0.8191420365705864</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.01545363769555</v>
+        <v>5.365011216125527</v>
       </c>
       <c r="D3" t="n">
-        <v>32.44647950331527</v>
+        <v>5.272552919288732</v>
       </c>
       <c r="E3" t="n">
-        <v>5.308409623324787</v>
+        <v>0.862616563790278</v>
       </c>
       <c r="F3" t="n">
-        <v>5.040874071203608</v>
+        <v>0.8191420365705864</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.390411289743</v>
+        <v>3.800941834583238</v>
       </c>
       <c r="D4" t="n">
-        <v>23.43009419794211</v>
+        <v>3.807390307165593</v>
       </c>
       <c r="E4" t="n">
-        <v>5.308409623324787</v>
+        <v>0.862616563790278</v>
       </c>
       <c r="F4" t="n">
-        <v>5.040874071203608</v>
+        <v>0.8191420365705864</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.84417995963714</v>
+        <v>3.874679243441035</v>
       </c>
       <c r="D5" t="n">
-        <v>24.20214555516597</v>
+        <v>3.932848652714471</v>
       </c>
       <c r="E5" t="n">
-        <v>5.308409623324787</v>
+        <v>0.862616563790278</v>
       </c>
       <c r="F5" t="n">
-        <v>5.040874071203608</v>
+        <v>0.8191420365705864</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.47300757885379</v>
+        <v>4.139363731563741</v>
       </c>
       <c r="D6" t="n">
-        <v>24.16550296428751</v>
+        <v>3.92689423169672</v>
       </c>
       <c r="E6" t="n">
-        <v>5.308409623324787</v>
+        <v>0.862616563790278</v>
       </c>
       <c r="F6" t="n">
-        <v>5.040874071203608</v>
+        <v>0.8191420365705864</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.28537184758781</v>
+        <v>3.94637292523302</v>
       </c>
       <c r="D7" t="n">
-        <v>25.22814740408399</v>
+        <v>4.099573953163648</v>
       </c>
       <c r="E7" t="n">
-        <v>5.308409623324787</v>
+        <v>0.862616563790278</v>
       </c>
       <c r="F7" t="n">
-        <v>5.040874071203608</v>
+        <v>0.8191420365705864</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
